--- a/alunos_02.xlsx
+++ b/alunos_02.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Matemática</t>
   </si>
@@ -108,6 +108,15 @@
     <t>Pedro</t>
   </si>
   <si>
+    <t>Vitor</t>
+  </si>
+  <si>
+    <t>Luiz</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
     <t>Renato</t>
   </si>
   <si>
@@ -126,6 +135,15 @@
     <t>Melissa</t>
   </si>
   <si>
+    <t>Flávia</t>
+  </si>
+  <si>
+    <t>Bia</t>
+  </si>
+  <si>
+    <t>Paloma</t>
+  </si>
+  <si>
     <t>Juliana</t>
   </si>
   <si>
@@ -166,6 +184,24 @@
   </si>
   <si>
     <t>Luan</t>
+  </si>
+  <si>
+    <t>Alisson</t>
+  </si>
+  <si>
+    <t>Sandro</t>
+  </si>
+  <si>
+    <t>Bianca</t>
+  </si>
+  <si>
+    <t>Luciana</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>Bruna</t>
   </si>
   <si>
     <t>Alunos_nome</t>
@@ -791,61 +827,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1480,7 +1516,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5">
         <v>51</v>
@@ -1537,7 +1573,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" s="5">
         <v>47</v>
@@ -1594,7 +1630,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C15" s="5">
         <v>47</v>
@@ -1708,7 +1744,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C17" s="5">
         <v>49</v>
@@ -1765,7 +1801,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5">
         <v>47</v>
@@ -1879,7 +1915,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5">
         <v>51</v>
@@ -1936,7 +1972,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C21" s="5">
         <v>51</v>
@@ -1993,7 +2029,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C22" s="5">
         <v>48</v>
@@ -2050,7 +2086,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5">
         <v>53</v>
@@ -2164,7 +2200,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C25" s="5">
         <v>50</v>
@@ -2280,7 +2316,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" s="5">
         <v>33</v>
@@ -2337,7 +2373,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C28" s="5">
         <v>51</v>
@@ -2394,7 +2430,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C29" s="5">
         <v>46</v>
@@ -2451,7 +2487,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C30" s="5">
         <v>42</v>
@@ -2565,7 +2601,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C32" s="5">
         <v>47</v>
@@ -2622,7 +2658,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C33" s="5">
         <v>44</v>
@@ -2679,7 +2715,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C34" s="5">
         <v>49</v>
@@ -2795,7 +2831,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C36" s="5">
         <v>50</v>
@@ -2852,7 +2888,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C37" s="5">
         <v>48</v>
@@ -2966,7 +3002,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C39" s="5">
         <v>47</v>
@@ -3021,42 +3057,102 @@
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B40" s="1"/>
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B41" s="1"/>
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B42" s="1"/>
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B43" s="1"/>
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B44" s="1"/>
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B45" s="1"/>
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B46" s="1"/>
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B47" s="1"/>
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
     </row>
   </sheetData>

--- a/alunos_02.xlsx
+++ b/alunos_02.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Matemática</t>
   </si>
@@ -108,15 +108,6 @@
     <t>Pedro</t>
   </si>
   <si>
-    <t>Vitor</t>
-  </si>
-  <si>
-    <t>Luiz</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
     <t>Renato</t>
   </si>
   <si>
@@ -135,15 +126,6 @@
     <t>Melissa</t>
   </si>
   <si>
-    <t>Flávia</t>
-  </si>
-  <si>
-    <t>Bia</t>
-  </si>
-  <si>
-    <t>Paloma</t>
-  </si>
-  <si>
     <t>Juliana</t>
   </si>
   <si>
@@ -184,24 +166,6 @@
   </si>
   <si>
     <t>Luan</t>
-  </si>
-  <si>
-    <t>Alisson</t>
-  </si>
-  <si>
-    <t>Sandro</t>
-  </si>
-  <si>
-    <t>Bianca</t>
-  </si>
-  <si>
-    <t>Luciana</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Bruna</t>
   </si>
   <si>
     <t>Alunos_nome</t>
@@ -827,61 +791,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1516,7 +1480,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="5">
         <v>51</v>
@@ -1573,7 +1537,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5">
         <v>47</v>
@@ -1630,7 +1594,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C15" s="5">
         <v>47</v>
@@ -1744,7 +1708,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5">
         <v>49</v>
@@ -1801,7 +1765,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5">
         <v>47</v>
@@ -1915,7 +1879,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5">
         <v>51</v>
@@ -1972,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="5">
         <v>51</v>
@@ -2029,7 +1993,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C22" s="5">
         <v>48</v>
@@ -2086,7 +2050,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C23" s="5">
         <v>53</v>
@@ -2200,7 +2164,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C25" s="5">
         <v>50</v>
@@ -2316,7 +2280,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5">
         <v>33</v>
@@ -2373,7 +2337,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C28" s="5">
         <v>51</v>
@@ -2430,7 +2394,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C29" s="5">
         <v>46</v>
@@ -2487,7 +2451,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C30" s="5">
         <v>42</v>
@@ -2601,7 +2565,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5">
         <v>47</v>
@@ -2658,7 +2622,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C33" s="5">
         <v>44</v>
@@ -2715,7 +2679,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C34" s="5">
         <v>49</v>
@@ -2831,7 +2795,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C36" s="5">
         <v>50</v>
@@ -2888,7 +2852,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C37" s="5">
         <v>48</v>
@@ -3002,7 +2966,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C39" s="5">
         <v>47</v>
@@ -3057,102 +3021,42 @@
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="B44" s="1"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3"/>
     </row>
   </sheetData>
